--- a/2024AIDataScienceGNRClub/Advanced Excel/dec14.xlsx
+++ b/2024AIDataScienceGNRClub/Advanced Excel/dec14.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989D9B8A-FABE-446D-B150-72C8BDCD6002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53E6C6F-4C84-49F4-B14D-F201EA00D06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{57F09C16-5EC0-4845-97CD-1ACAC51F7ECF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{57F09C16-5EC0-4845-97CD-1ACAC51F7ECF}"/>
   </bookViews>
   <sheets>
     <sheet name="24_DS_GNR_Club" sheetId="1" r:id="rId1"/>
+    <sheet name="dec21" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="26">
   <si>
     <t>Abc</t>
   </si>
@@ -63,13 +64,58 @@
   </si>
   <si>
     <t>abcd</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t>Tue</t>
+  </si>
+  <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>Fri</t>
+  </si>
+  <si>
+    <t>Sat</t>
+  </si>
+  <si>
+    <t>Sun</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,6 +135,12 @@
     <font>
       <sz val="36"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -148,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -160,11 +212,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,11 +552,11 @@
       <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
@@ -526,17 +581,17 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="2"/>
@@ -571,4 +626,761 @@
     <brk id="10" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEECE7D7-AFAD-4E48-8070-FED642136764}">
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8">
+        <v>45647</v>
+      </c>
+      <c r="E1">
+        <v>1</v>
+      </c>
+      <c r="F1" s="9">
+        <v>45343</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8">
+        <v>45648</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="10">
+        <v>45344</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="8">
+        <v>45649</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" s="10">
+        <v>45345</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="8">
+        <v>45650</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8">
+        <v>45346</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8">
+        <v>45651</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8">
+        <v>45347</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8">
+        <v>45652</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6" s="8">
+        <v>45348</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8">
+        <v>45653</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7" s="8">
+        <v>45349</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8" s="8">
+        <v>45654</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8" s="8">
+        <v>45350</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9" s="8">
+        <v>45655</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9" s="8">
+        <v>45351</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" s="8">
+        <v>45656</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10" s="8">
+        <v>45352</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11" s="8">
+        <v>45657</v>
+      </c>
+      <c r="E11">
+        <v>11</v>
+      </c>
+      <c r="F11" s="8">
+        <v>45353</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12" s="8">
+        <v>45658</v>
+      </c>
+      <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="F12" s="8">
+        <v>45354</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13" s="8">
+        <v>45659</v>
+      </c>
+      <c r="E13">
+        <v>13</v>
+      </c>
+      <c r="F13" s="8">
+        <v>45355</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>14</v>
+      </c>
+      <c r="D14" s="8">
+        <v>45660</v>
+      </c>
+      <c r="E14">
+        <v>14</v>
+      </c>
+      <c r="F14" s="8">
+        <v>45356</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>15</v>
+      </c>
+      <c r="D15" s="8">
+        <v>45661</v>
+      </c>
+      <c r="E15">
+        <v>15</v>
+      </c>
+      <c r="F15" s="8">
+        <v>45357</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
+      <c r="D16" s="8">
+        <v>45662</v>
+      </c>
+      <c r="E16">
+        <v>16</v>
+      </c>
+      <c r="F16" s="8">
+        <v>45358</v>
+      </c>
+      <c r="G16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>17</v>
+      </c>
+      <c r="D17" s="8">
+        <v>45663</v>
+      </c>
+      <c r="E17">
+        <v>17</v>
+      </c>
+      <c r="F17" s="8">
+        <v>45359</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>18</v>
+      </c>
+      <c r="D18" s="8">
+        <v>45664</v>
+      </c>
+      <c r="E18">
+        <v>18</v>
+      </c>
+      <c r="F18" s="8">
+        <v>45360</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>19</v>
+      </c>
+      <c r="D19" s="8">
+        <v>45665</v>
+      </c>
+      <c r="E19">
+        <v>19</v>
+      </c>
+      <c r="F19" s="8">
+        <v>45361</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+      <c r="D20" s="8">
+        <v>45666</v>
+      </c>
+      <c r="E20">
+        <v>20</v>
+      </c>
+      <c r="F20" s="8">
+        <v>45362</v>
+      </c>
+      <c r="G20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>21</v>
+      </c>
+      <c r="D21" s="8">
+        <v>45667</v>
+      </c>
+      <c r="E21">
+        <v>21</v>
+      </c>
+      <c r="F21" s="8">
+        <v>45363</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>22</v>
+      </c>
+      <c r="D22" s="8">
+        <v>45668</v>
+      </c>
+      <c r="E22">
+        <v>22</v>
+      </c>
+      <c r="F22" s="8">
+        <v>45364</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23">
+        <v>23</v>
+      </c>
+      <c r="D23" s="8">
+        <v>45669</v>
+      </c>
+      <c r="E23">
+        <v>23</v>
+      </c>
+      <c r="F23" s="8">
+        <v>45365</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24">
+        <v>24</v>
+      </c>
+      <c r="D24" s="8">
+        <v>45670</v>
+      </c>
+      <c r="E24">
+        <v>24</v>
+      </c>
+      <c r="F24" s="8">
+        <v>45366</v>
+      </c>
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25">
+        <v>25</v>
+      </c>
+      <c r="D25" s="8">
+        <v>45671</v>
+      </c>
+      <c r="E25">
+        <v>25</v>
+      </c>
+      <c r="F25" s="8">
+        <v>45367</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26">
+        <v>26</v>
+      </c>
+      <c r="D26" s="8">
+        <v>45672</v>
+      </c>
+      <c r="E26">
+        <v>26</v>
+      </c>
+      <c r="F26" s="8">
+        <v>45368</v>
+      </c>
+      <c r="G26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27">
+        <v>27</v>
+      </c>
+      <c r="D27" s="8">
+        <v>45673</v>
+      </c>
+      <c r="E27">
+        <v>27</v>
+      </c>
+      <c r="F27" s="8">
+        <v>45369</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28">
+        <v>28</v>
+      </c>
+      <c r="D28" s="8">
+        <v>45674</v>
+      </c>
+      <c r="E28">
+        <v>28</v>
+      </c>
+      <c r="F28" s="8">
+        <v>45370</v>
+      </c>
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D29" s="8">
+        <v>45675</v>
+      </c>
+      <c r="E29">
+        <v>29</v>
+      </c>
+      <c r="F29" s="8">
+        <v>45371</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D30" s="8">
+        <v>45676</v>
+      </c>
+      <c r="E30">
+        <v>30</v>
+      </c>
+      <c r="F30" s="8">
+        <v>45372</v>
+      </c>
+      <c r="G30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D31" s="8">
+        <v>45677</v>
+      </c>
+      <c r="E31">
+        <v>31</v>
+      </c>
+      <c r="F31" s="8">
+        <v>45373</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D32" s="8">
+        <v>45678</v>
+      </c>
+      <c r="E32">
+        <v>32</v>
+      </c>
+      <c r="F32" s="8">
+        <v>45374</v>
+      </c>
+      <c r="G32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D33" s="8">
+        <v>45679</v>
+      </c>
+      <c r="E33">
+        <v>33</v>
+      </c>
+      <c r="F33" s="8">
+        <v>45375</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D34" s="8">
+        <v>45680</v>
+      </c>
+      <c r="E34">
+        <v>34</v>
+      </c>
+      <c r="F34" s="8">
+        <v>45376</v>
+      </c>
+      <c r="G34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D35" s="8">
+        <v>45681</v>
+      </c>
+      <c r="E35">
+        <v>35</v>
+      </c>
+      <c r="F35" s="8">
+        <v>45377</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D36" s="8">
+        <v>45682</v>
+      </c>
+      <c r="E36">
+        <v>36</v>
+      </c>
+      <c r="F36" s="8">
+        <v>45378</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>